--- a/diseases/d032/2005-2009.xlsx
+++ b/diseases/d032/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>14</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.02925709302693968</v>
       </c>
@@ -1457,9 +1451,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2001,9 +1992,6 @@
       <c r="O9" t="n">
         <v>6</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.01253875415440272</v>
       </c>
@@ -2149,9 +2137,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2693,9 +2678,6 @@
       <c r="O13" t="n">
         <v>11</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.02298771594973832</v>
       </c>
@@ -2841,9 +2823,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3385,9 +3364,6 @@
       <c r="O17" t="n">
         <v>15</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.0313468853860068</v>
       </c>
@@ -3533,9 +3509,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4077,9 +4050,6 @@
       <c r="O21" t="n">
         <v>11</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.02298771594973832</v>
       </c>
@@ -4225,9 +4195,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4769,9 +4736,6 @@
       <c r="O25" t="n">
         <v>20</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.0417958471813424</v>
       </c>
@@ -4917,9 +4881,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -5461,9 +5422,6 @@
       <c r="O29" t="n">
         <v>19</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.03970605482227528</v>
       </c>
@@ -5609,9 +5567,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6153,9 +6108,6 @@
       <c r="O33" t="n">
         <v>11</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.02298771594973832</v>
       </c>
@@ -6301,9 +6253,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6845,9 +6794,6 @@
       <c r="O37" t="n">
         <v>19</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.03970605482227528</v>
       </c>
@@ -6993,9 +6939,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7537,9 +7480,6 @@
       <c r="O41" t="n">
         <v>10</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.0208979235906712</v>
       </c>
@@ -7685,9 +7625,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8229,9 +8166,6 @@
       <c r="O45" t="n">
         <v>12</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.02507750830880544</v>
       </c>
@@ -8377,9 +8311,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -8921,9 +8852,6 @@
       <c r="O49" t="n">
         <v>10</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.0208979235906712</v>
       </c>
@@ -9069,9 +8997,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9613,9 +9538,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -10009,9 +9931,6 @@
       <c r="O55" t="n">
         <v>9</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.01874745444720084</v>
       </c>
@@ -10157,9 +10076,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10701,9 +10617,6 @@
       <c r="O59" t="n">
         <v>3</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.006249151482400281</v>
       </c>
@@ -10849,9 +10762,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -11393,9 +11303,6 @@
       <c r="O63" t="n">
         <v>16</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.03332880790613483</v>
       </c>
@@ -11541,9 +11448,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12085,9 +11989,6 @@
       <c r="O67" t="n">
         <v>20</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.04166100988266853</v>
       </c>
@@ -12233,9 +12134,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -12777,9 +12675,6 @@
       <c r="O71" t="n">
         <v>18</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.03749490889440169</v>
       </c>
@@ -12925,9 +12820,6 @@
       <c r="O72" t="n">
         <v>1</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -13469,9 +13361,6 @@
       <c r="O75" t="n">
         <v>15</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.0312457574120014</v>
       </c>
@@ -13617,9 +13506,6 @@
       <c r="O76" t="n">
         <v>1</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -14161,9 +14047,6 @@
       <c r="O79" t="n">
         <v>23</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.04791016136506882</v>
       </c>
@@ -14309,9 +14192,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -14853,9 +14733,6 @@
       <c r="O83" t="n">
         <v>29</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.06040846432986937</v>
       </c>
@@ -15001,9 +14878,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -15545,9 +15419,6 @@
       <c r="O87" t="n">
         <v>30</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.0624915148240028</v>
       </c>
@@ -15693,9 +15564,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -16237,9 +16105,6 @@
       <c r="O91" t="n">
         <v>22</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.04582711087093538</v>
       </c>
@@ -16385,9 +16250,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -16929,9 +16791,6 @@
       <c r="O95" t="n">
         <v>19</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.03957795938853511</v>
       </c>
@@ -17077,9 +16936,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -17621,9 +17477,6 @@
       <c r="O99" t="n">
         <v>11</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.02291355543546769</v>
       </c>
@@ -17769,9 +17622,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -18313,9 +18163,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -18709,9 +18556,6 @@
       <c r="O105" t="n">
         <v>9</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.01868067969487019</v>
       </c>
@@ -19005,9 +18849,6 @@
       <c r="O107" t="n">
         <v>12</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.02490757292649359</v>
       </c>
@@ -19301,9 +19142,6 @@
       <c r="O109" t="n">
         <v>9</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.01868067969487019</v>
       </c>
@@ -19597,9 +19435,6 @@
       <c r="O111" t="n">
         <v>9</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.01868067969487019</v>
       </c>
@@ -19893,9 +19728,6 @@
       <c r="O113" t="n">
         <v>15</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.03113446615811699</v>
       </c>
@@ -20189,9 +20021,6 @@
       <c r="O115" t="n">
         <v>11</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.02283194184928579</v>
       </c>
@@ -20485,9 +20314,6 @@
       <c r="O117" t="n">
         <v>9</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.01868067969487019</v>
       </c>
@@ -20781,9 +20607,6 @@
       <c r="O119" t="n">
         <v>10</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.02075631077207799</v>
       </c>
@@ -21077,9 +20900,6 @@
       <c r="O121" t="n">
         <v>5</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.010378155386039</v>
       </c>
@@ -21373,9 +21193,6 @@
       <c r="O123" t="n">
         <v>5</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.010378155386039</v>
       </c>
@@ -21669,9 +21486,6 @@
       <c r="O125" t="n">
         <v>2</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.004151262154415599</v>
       </c>
@@ -21965,9 +21779,6 @@
       <c r="O127" t="n">
         <v>5</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.010378155386039</v>
       </c>
@@ -22261,9 +22072,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -22657,9 +22465,6 @@
       <c r="O131" t="n">
         <v>9</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.01861177153603757</v>
       </c>
@@ -22953,9 +22758,6 @@
       <c r="O133" t="n">
         <v>3</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.006203923845345857</v>
       </c>
@@ -23249,9 +23051,6 @@
       <c r="O135" t="n">
         <v>5</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.01033987307557643</v>
       </c>
@@ -23545,9 +23344,6 @@
       <c r="O137" t="n">
         <v>10</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.02067974615115285</v>
       </c>
@@ -23841,9 +23637,6 @@
       <c r="O139" t="n">
         <v>7</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.014475822305807</v>
       </c>
@@ -24137,9 +23930,6 @@
       <c r="O141" t="n">
         <v>1</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -24433,9 +24223,6 @@
       <c r="O143" t="n">
         <v>6</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.01240784769069171</v>
       </c>
@@ -24729,9 +24516,6 @@
       <c r="O145" t="n">
         <v>2</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -25025,9 +24809,6 @@
       <c r="O147" t="n">
         <v>7</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.014475822305807</v>
       </c>
@@ -25321,9 +25102,6 @@
       <c r="O149" t="n">
         <v>1</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -25617,9 +25395,6 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -25913,9 +25688,6 @@
       <c r="O153" t="n">
         <v>6</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.01240784769069171</v>
       </c>
@@ -26209,9 +25981,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -26605,9 +26374,6 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -26753,9 +26519,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -27297,9 +27060,6 @@
       <c r="O161" t="n">
         <v>1</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -27445,9 +27205,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -27989,9 +27746,6 @@
       <c r="O165" t="n">
         <v>4</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.008239491278153453</v>
       </c>
@@ -28137,9 +27891,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -28681,9 +28432,6 @@
       <c r="O169" t="n">
         <v>3</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.00617961845861509</v>
       </c>
@@ -28829,9 +28577,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -29373,9 +29118,6 @@
       <c r="O173" t="n">
         <v>2</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -29521,9 +29263,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -30065,9 +29804,6 @@
       <c r="O177" t="n">
         <v>1</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -30213,9 +29949,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -30757,9 +30490,6 @@
       <c r="O181" t="n">
         <v>3</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.00617961845861509</v>
       </c>
@@ -30905,9 +30635,6 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
@@ -31449,9 +31176,6 @@
       <c r="O185" t="n">
         <v>2</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -31597,9 +31321,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -32141,9 +31862,6 @@
       <c r="O189" t="n">
         <v>2</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -32289,9 +32007,6 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -32833,9 +32548,6 @@
       <c r="O193" t="n">
         <v>1</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -32981,9 +32693,6 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -33525,9 +33234,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -33673,9 +33379,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -34217,9 +33920,6 @@
       <c r="O201" t="n">
         <v>4</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.008239491278153453</v>
       </c>
@@ -34363,9 +34063,6 @@
         <v>0</v>
       </c>
       <c r="O202" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q202" t="n">
         <v>0</v>
       </c>
       <c r="R202" t="n">
